--- a/examples/stc89c52rc-usb-isp/bom/stc89c52rc-usb-isp-bom.xlsx
+++ b/examples/stc89c52rc-usb-isp/bom/stc89c52rc-usb-isp-bom.xlsx
@@ -273,7 +273,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1.0-P1.7</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2.0-P2.7</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>56.642</v>
+        <v>28.051</v>
       </c>
       <c r="C2">
-        <v>53.038</v>
+        <v>72.592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>58.928</v>
+        <v>34.655</v>
       </c>
       <c r="C3">
-        <v>70.564</v>
+        <v>68.782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>64.516</v>
+        <v>40.243</v>
       </c>
       <c r="C4">
-        <v>74.628</v>
+        <v>72.846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>62.23</v>
+        <v>75.549</v>
       </c>
       <c r="C5">
-        <v>57.102</v>
+        <v>5.79</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>66.802</v>
+        <v>78.597</v>
       </c>
       <c r="C6">
-        <v>57.102</v>
+        <v>19.506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>71.374</v>
+        <v>34.147</v>
       </c>
       <c r="C7">
-        <v>57.102</v>
+        <v>29.412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>75.946</v>
+        <v>38.719</v>
       </c>
       <c r="C8">
-        <v>57.102</v>
+        <v>29.412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>5.08</v>
+        <v>59.547</v>
       </c>
       <c r="C9">
-        <v>30.94</v>
+        <v>11.886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>4.064</v>
+        <v>32.115</v>
       </c>
       <c r="C10">
-        <v>27.13</v>
+        <v>37.794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>69.088</v>
+        <v>86.725</v>
       </c>
       <c r="C11">
-        <v>74.628</v>
+        <v>69.036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>74.676</v>
+        <v>90.027</v>
       </c>
       <c r="C12">
-        <v>74.374</v>
+        <v>72.592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>7.62</v>
+        <v>22.717</v>
       </c>
       <c r="C13">
-        <v>48.466</v>
+        <v>64.464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>13.462</v>
+        <v>9.001</v>
       </c>
       <c r="C14">
-        <v>30.432</v>
+        <v>50.748</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>15.494</v>
+        <v>101.711</v>
       </c>
       <c r="C15">
-        <v>56.594</v>
+        <v>72.338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>33.274</v>
+        <v>93.583</v>
       </c>
       <c r="C16">
-        <v>3.762</v>
+        <v>46.684</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1.0-P1.7</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
     </row>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>55.118</v>
+        <v>97.647</v>
       </c>
       <c r="C17">
-        <v>48.212</v>
+        <v>24.84</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2.0-P2.7</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
     </row>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>20.32</v>
+        <v>64.881</v>
       </c>
       <c r="C18">
-        <v>43.386</v>
+        <v>15.95</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>24.638</v>
+        <v>19.415</v>
       </c>
       <c r="C19">
-        <v>57.356</v>
+        <v>64.718</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>30.226</v>
+        <v>52.689</v>
       </c>
       <c r="C20">
-        <v>54.562</v>
+        <v>13.156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>28.702</v>
+        <v>76.311</v>
       </c>
       <c r="C21">
-        <v>14.938</v>
+        <v>48.97</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>37.338</v>
+        <v>21.193</v>
       </c>
       <c r="C22">
-        <v>38.052</v>
+        <v>53.796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>47.244</v>
+        <v>23.733</v>
       </c>
       <c r="C23">
-        <v>28.908</v>
+        <v>18.236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>73.152</v>
+        <v>70.723</v>
       </c>
       <c r="C24">
-        <v>46.942</v>
+        <v>14.68</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>8.89</v>
+        <v>24.749</v>
       </c>
       <c r="C25">
-        <v>39.068</v>
+        <v>27.888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
